--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487146_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487146_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.8575</v>
+        <v>6.9624</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0001</v>
+        <v>1.8986</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8574</v>
+        <v>5.0638</v>
       </c>
       <c r="G2" t="n">
         <v>4.065</v>
@@ -610,13 +610,13 @@
         <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5416</v>
+        <v>1.6465</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6941000000000001</v>
+        <v>-0.4075</v>
       </c>
       <c r="U2" t="n">
-        <v>3.8475</v>
+        <v>2.054</v>
       </c>
       <c r="V2" t="n">
         <v>0.2859</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8146</v>
+        <v>6.5166</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9503</v>
+        <v>3.2507</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8643</v>
+        <v>3.2658</v>
       </c>
       <c r="G3" t="n">
         <v>3.7004</v>
@@ -688,13 +688,13 @@
         <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1138</v>
+        <v>-0.4118</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3682</v>
+        <v>-1.0678</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2545</v>
+        <v>0.656</v>
       </c>
       <c r="V3" t="n">
         <v>2.4559</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6836</v>
+        <v>3.9037</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2943</v>
+        <v>1.5947</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3893</v>
+        <v>2.309</v>
       </c>
       <c r="G4" t="n">
         <v>-1.444</v>
@@ -766,13 +766,13 @@
         <v>2.8951</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6022</v>
+        <v>-0.3821</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1898</v>
+        <v>-0.8893</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5876</v>
+        <v>0.5073</v>
       </c>
       <c r="V4" t="n">
         <v>3.0277</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0611</v>
+        <v>3.5093</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4961</v>
+        <v>2.5963</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.913</v>
       </c>
       <c r="G5" t="n">
         <v>0.771</v>
@@ -844,13 +844,13 @@
         <v>2.5091</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2539</v>
+        <v>-0.8057</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0708</v>
+        <v>-0.9706</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1831</v>
+        <v>0.1649</v>
       </c>
       <c r="V5" t="n">
         <v>1.228</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8821</v>
+        <v>1.2232</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.233</v>
+        <v>-1.1328</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1151</v>
+        <v>2.356</v>
       </c>
       <c r="G6" t="n">
         <v>1.4999</v>
@@ -922,13 +922,13 @@
         <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2703</v>
+        <v>0.0707</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7139</v>
+        <v>-0.6137</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4435</v>
+        <v>0.6844</v>
       </c>
       <c r="V6" t="n">
         <v>-1.3125</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.155</v>
+        <v>0.0549</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4125</v>
+        <v>-3.5127</v>
       </c>
       <c r="F7" t="n">
         <v>3.5675</v>
@@ -1000,10 +1000,10 @@
         <v>2.8951</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2974</v>
+        <v>0.1973</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8196</v>
+        <v>-0.9197</v>
       </c>
       <c r="U7" t="n">
         <v>1.117</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3842</v>
+        <v>-0.5913</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1419</v>
+        <v>-2.2787</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7577</v>
+        <v>1.6874</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.244</v>
+        <v>-0.5285</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8653</v>
+        <v>0.4647</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3788</v>
+        <v>-0.9932</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5093</v>
+        <v>-0.0019</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6314</v>
+        <v>0.6985</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>-0.7004</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7347</v>
+        <v>-0.5266</v>
       </c>
       <c r="N8" t="n">
         <v>-0.2338</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5009</v>
+        <v>-0.2928</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>-0.579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4389</v>
+        <v>0.2304</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0462</v>
+        <v>-0.6325</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4852</v>
+        <v>0.8629</v>
       </c>
       <c r="V8" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5717</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0325</v>
+        <v>-0.8383</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4789</v>
+        <v>-1.5425</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4464</v>
+        <v>0.7042</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5285</v>
+        <v>-2.244</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4647</v>
+        <v>-0.8653</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9932</v>
+        <v>-1.3788</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0019</v>
+        <v>-0.5093</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6985</v>
+        <v>-0.6314</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7004</v>
+        <v>0.1221</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5266</v>
+        <v>-1.7347</v>
       </c>
       <c r="N9" t="n">
         <v>-0.2338</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2928</v>
+        <v>-1.5009</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.579</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-1.158</v>
       </c>
       <c r="R9" t="n">
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2109</v>
+        <v>-0.0152</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8328</v>
+        <v>-0.4468</v>
       </c>
       <c r="U9" t="n">
-        <v>0.622</v>
+        <v>0.4316</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0.5717</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.545</v>
+        <v>-1.2362</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5292</v>
+        <v>-1.3834</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0158</v>
+        <v>0.1472</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7816</v>
+        <v>0.3452</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5195</v>
+        <v>-0.4802</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.262</v>
+        <v>0.8254</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7333</v>
+        <v>1.6799</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0414</v>
+        <v>0.4347</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6919</v>
+        <v>1.2453</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5149</v>
+        <v>-1.3347</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5609</v>
+        <v>-0.9149</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9539</v>
+        <v>-0.4199</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.386</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R10" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3774</v>
+        <v>-0.0373</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2974</v>
+        <v>-0.4541</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08</v>
+        <v>0.4167</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7309</v>
+        <v>-1.4647</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5837</v>
+        <v>-0.5292</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1472</v>
+        <v>-0.9355</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3452</v>
+        <v>-0.7816</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4802</v>
+        <v>-0.5195</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8254</v>
+        <v>-0.262</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6799</v>
+        <v>0.7333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4347</v>
+        <v>0.0414</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2453</v>
+        <v>0.6919</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3347</v>
+        <v>-1.5149</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9149</v>
+        <v>-0.5609</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4199</v>
+        <v>-0.9539</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5441</v>
+        <v>-0.386</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5321</v>
+        <v>-0.2971</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6544</v>
+        <v>-0.2974</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1223</v>
+        <v>0.0003</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0787</v>
+        <v>-4.3569</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6198</v>
+        <v>-5.2192</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5411</v>
+        <v>0.8623</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0465</v>
@@ -1390,13 +1390,13 @@
         <v>0.579</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3953</v>
+        <v>0.3265</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4759</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0806</v>
+        <v>0.4019</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2859</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.6826</v>
+        <v>13.6827</v>
       </c>
       <c r="E13" t="n">
         <v>-6.2582</v>
       </c>
       <c r="F13" t="n">
-        <v>19.9408</v>
+        <v>19.9407</v>
       </c>
       <c r="G13" t="n">
         <v>1.7083</v>
@@ -1447,16 +1447,16 @@
         <v>9.582999999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2252999999999998</v>
+        <v>0.2253000000000003</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.100000000000001</v>
+        <v>-8.099999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>0.9324999999999997</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.032500000000002</v>
+        <v>-9.032499999999999</v>
       </c>
       <c r="P13" t="n">
         <v>4.825000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>21.2309</v>
       </c>
       <c r="S13" t="n">
-        <v>0.522</v>
+        <v>0.5222000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.774900000000001</v>
+        <v>-6.774700000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>7.2971</v>
+        <v>7.297000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>6.6271</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
+          <t>P. MOLINA MATA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7571</v>
+        <v>1.4291</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8938</v>
+        <v>0.6121</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1367</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1536</v>
+        <v>3.4364</v>
       </c>
       <c r="H14" t="n">
-        <v>2.188</v>
+        <v>-1.5618</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9657</v>
+        <v>4.9981</v>
       </c>
       <c r="J14" t="n">
-        <v>7.1076</v>
+        <v>4.1367</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2498</v>
+        <v>-0.4865</v>
       </c>
       <c r="L14" t="n">
-        <v>3.8579</v>
+        <v>4.6233</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.954</v>
+        <v>-0.7004</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0618</v>
+        <v>-1.0752</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1078</v>
+        <v>0.3748</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.3161</v>
+        <v>-0.579</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.8252</v>
+        <v>-2.8951</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5091</v>
+        <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9895</v>
+        <v>-0.2003</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3886</v>
+        <v>-0.9154</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3781</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.0699</v>
+        <v>-1.228</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.0699</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MOLINA MATA</t>
+          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0147</v>
+        <v>0.9015</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4118</v>
+        <v>1.4932</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6029</v>
+        <v>-0.5918</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4364</v>
+        <v>6.1536</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5618</v>
+        <v>2.188</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9981</v>
+        <v>3.9657</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1367</v>
+        <v>7.1076</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4865</v>
+        <v>3.2498</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6233</v>
+        <v>3.8579</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7004</v>
+        <v>-0.954</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0752</v>
+        <v>-1.0618</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3748</v>
+        <v>0.1078</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.579</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>-4.8252</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3161</v>
+        <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6147</v>
+        <v>0.1338</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1157</v>
+        <v>-0.7892</v>
       </c>
       <c r="U15" t="n">
-        <v>0.501</v>
+        <v>0.923</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.228</v>
+        <v>-3.0699</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5138</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3799</v>
+        <v>-0.1925</v>
       </c>
       <c r="E16" t="n">
         <v>-1.4853</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1054</v>
+        <v>1.2928</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9231</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.306</v>
+        <v>-0.1186</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1639</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1421</v>
+        <v>0.0453</v>
       </c>
       <c r="V16" t="n">
         <v>0.6562</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. AZKOAGA BENDEJACQ</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8628</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1085</v>
+        <v>-0.8828</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2457</v>
+        <v>0.1232</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0735</v>
+        <v>-0.5696</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0735</v>
+        <v>-0.384</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.1856</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.645</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.6778</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.0328</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0735</v>
+        <v>-1.2146</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0735</v>
+        <v>-1.0618</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.1528</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7371</v>
+        <v>-0.193</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2915</v>
+        <v>0.003</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1785</v>
+        <v>-0.5628</v>
       </c>
       <c r="U17" t="n">
-        <v>0.47</v>
+        <v>0.5658</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9807</v>
+        <v>-0.9316</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7827</v>
+        <v>-0.6605</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.198</v>
+        <v>-0.2711</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5696</v>
+        <v>-1.0202</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.384</v>
+        <v>-4.1412</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1856</v>
+        <v>3.121</v>
       </c>
       <c r="J18" t="n">
-        <v>0.645</v>
+        <v>0.6148</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6778</v>
+        <v>-2.6654</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0328</v>
+        <v>3.2802</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2146</v>
+        <v>-1.635</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0618</v>
+        <v>-1.4758</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1528</v>
+        <v>-0.1592</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2181</v>
+        <v>0.3745</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4627</v>
+        <v>-0.3103</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2446</v>
+        <v>0.6848</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>A. AZKOAGA BENDEJACQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0197</v>
+        <v>-1.0502</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6812</v>
+        <v>-2.1085</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3385</v>
+        <v>1.0583</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2858</v>
+        <v>-0.0735</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2711</v>
+        <v>-0.0735</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5569</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5547</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6921</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8625</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2689</v>
+        <v>-0.0735</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9632</v>
+        <v>-0.0735</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3056</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.158</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>3.0881</v>
+        <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2935</v>
+        <v>0.1041</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5916</v>
+        <v>-0.1785</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2981</v>
+        <v>0.2826</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1701</v>
+        <v>0.6562</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4559</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0456</v>
+        <v>-1.0941</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5604</v>
+        <v>-0.3808</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4852</v>
+        <v>-0.7133</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0202</v>
+        <v>0.2858</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.1412</v>
+        <v>-0.2711</v>
       </c>
       <c r="I20" t="n">
-        <v>3.121</v>
+        <v>0.5569</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6148</v>
+        <v>2.5547</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.6654</v>
+        <v>1.6921</v>
       </c>
       <c r="L20" t="n">
-        <v>3.2802</v>
+        <v>0.8625</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.635</v>
+        <v>-2.2689</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4758</v>
+        <v>-1.9632</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1592</v>
+        <v>-0.3056</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>1.158</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>3.0881</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2604</v>
+        <v>-0.3678</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2102</v>
+        <v>-1.2912</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4706</v>
+        <v>0.9234</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2859</v>
+        <v>-2.1701</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2859</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. DIEZ TIDALA</t>
+          <t>A. LOPEZ BRETON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4634</v>
+        <v>-1.3949</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4985</v>
+        <v>-2.5277</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0351</v>
+        <v>1.1328</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8395</v>
+        <v>-0.2554</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4668</v>
+        <v>-0.591</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3727</v>
+        <v>0.3356</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0614</v>
+        <v>0.1383</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0207</v>
+        <v>0.0569</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0407</v>
+        <v>0.0814</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9009</v>
+        <v>-0.3936</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4875</v>
+        <v>-0.6478</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4134</v>
+        <v>0.2542</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
         <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.431</v>
+        <v>0.0185</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5949</v>
+        <v>-0.6514</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1639</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LOPEZ BRETON</t>
+          <t>L. DIEZ TIDALA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7221</v>
+        <v>-1.4634</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8281</v>
+        <v>-1.4985</v>
       </c>
       <c r="F22" t="n">
-        <v>1.106</v>
+        <v>0.0351</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2554</v>
+        <v>-0.8395</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.591</v>
+        <v>-0.4668</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3356</v>
+        <v>-0.3727</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1383</v>
+        <v>0.0614</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0569</v>
+        <v>0.0207</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0814</v>
+        <v>0.0407</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3936</v>
+        <v>-0.9009</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6478</v>
+        <v>-0.4875</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2542</v>
+        <v>-0.4134</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.158</v>
+        <v>-0.193</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
         <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3087</v>
+        <v>-0.431</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9518</v>
+        <v>-0.5949</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6431</v>
+        <v>0.1639</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.08450000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. ALBISU ASTIGARRAGA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4629</v>
+        <v>-4.5102</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.3291</v>
+        <v>-6.0726</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8663</v>
+        <v>1.5624</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.7656</v>
+        <v>-4.1372</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6571</v>
+        <v>-3.134</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1085</v>
+        <v>-1.0032</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.639</v>
+        <v>-3.1633</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0092</v>
+        <v>-1.9252</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6297</v>
+        <v>-1.2381</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1266</v>
+        <v>-0.9739</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6478</v>
+        <v>-1.2087</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5212</v>
+        <v>0.2349</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.386</v>
+        <v>0.386</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2604</v>
+        <v>-0.1451</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7601</v>
+        <v>-0.9792</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0205</v>
+        <v>0.8341</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5717</v>
+        <v>-0.614</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5717</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>P. ALBISU ASTIGARRAGA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5172</v>
+        <v>-4.6166</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.9725</v>
+        <v>-6.4293</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4553</v>
+        <v>1.8127</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1372</v>
+        <v>-3.7656</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.134</v>
+        <v>-1.6571</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0032</v>
+        <v>-2.1085</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1633</v>
+        <v>-3.639</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9252</v>
+        <v>-1.0092</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2381</v>
+        <v>-2.6297</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.9739</v>
+        <v>-0.1266</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2087</v>
+        <v>-0.6478</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2349</v>
+        <v>0.5212</v>
       </c>
       <c r="P24" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3161</v>
+        <v>1.5441</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.152</v>
+        <v>0.1068</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8791</v>
+        <v>-0.8602</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7271</v>
+        <v>0.967</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.614</v>
+        <v>-0.5717</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.614</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="25">
@@ -2365,10 +2365,10 @@
         <v>-19.9407</v>
       </c>
       <c r="F25" t="n">
-        <v>6.2583</v>
+        <v>6.258100000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.7083</v>
+        <v>-1.708299999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-10.5158</v>
@@ -2377,10 +2377,10 @@
         <v>8.807499999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>8.0999</v>
+        <v>8.099900000000002</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9323999999999999</v>
+        <v>-0.9324000000000003</v>
       </c>
       <c r="L25" t="n">
         <v>9.032500000000001</v>
@@ -2395,7 +2395,7 @@
         <v>-0.2249999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.825200000000001</v>
+        <v>-4.8252</v>
       </c>
       <c r="Q25" t="n">
         <v>-21.2308</v>
@@ -2404,22 +2404,22 @@
         <v>16.4055</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5221999999999998</v>
+        <v>-0.5221</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.297099999999999</v>
+        <v>-7.297</v>
       </c>
       <c r="U25" t="n">
-        <v>6.774900000000001</v>
+        <v>6.775</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.627199999999999</v>
+        <v>-6.6272</v>
       </c>
       <c r="W25" t="n">
         <v>0.4873</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.114299999999999</v>
+        <v>-7.114300000000001</v>
       </c>
     </row>
   </sheetData>
